--- a/backend/data/financials_by_company/0657.HK.xlsx
+++ b/backend/data/financials_by_company/0657.HK.xlsx
@@ -3785,7 +3785,7 @@
         <v>-8749000</v>
       </c>
       <c r="BN2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO2" t="n">
         <v>4.52</v>
@@ -4037,7 +4037,7 @@
         <v>0</v>
       </c>
       <c r="EF2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG2" t="n">
         <v>0.00018000044</v>
